--- a/fhir/finnish-smart/StructureDefinition-fi-smart-condition.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-condition.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-condition.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$38</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1232,21 +1229,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1594,7 +1576,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1712,7 +1694,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -1832,7 +1814,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -1950,7 +1932,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2070,7 +2052,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2190,7 +2172,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2310,7 +2292,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2430,7 +2412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2550,7 +2532,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -2672,7 +2654,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -2794,7 +2776,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -2813,7 +2795,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -2914,7 +2896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>171</v>
       </c>
@@ -2933,7 +2915,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>92</v>
@@ -3034,7 +3016,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>182</v>
       </c>
@@ -3053,7 +3035,7 @@
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>79</v>
@@ -3154,7 +3136,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>192</v>
       </c>
@@ -3274,7 +3256,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>202</v>
       </c>
@@ -3287,13 +3269,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>79</v>
@@ -3394,7 +3376,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>216</v>
       </c>
@@ -3514,7 +3496,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>225</v>
       </c>
@@ -3533,7 +3515,7 @@
         <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
@@ -3634,7 +3616,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>235</v>
       </c>
@@ -3754,7 +3736,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -3874,7 +3856,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>253</v>
       </c>
@@ -3994,7 +3976,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>260</v>
       </c>
@@ -4112,7 +4094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>267</v>
       </c>
@@ -4230,7 +4212,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>273</v>
       </c>
@@ -4348,7 +4330,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>279</v>
       </c>
@@ -4466,7 +4448,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>285</v>
       </c>
@@ -4584,7 +4566,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>291</v>
       </c>
@@ -4704,7 +4686,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>294</v>
       </c>
@@ -4826,7 +4808,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>299</v>
       </c>
@@ -4944,7 +4926,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>306</v>
       </c>
@@ -5062,7 +5044,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>311</v>
       </c>
@@ -5180,7 +5162,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>317</v>
       </c>
@@ -5300,7 +5282,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>323</v>
       </c>
@@ -5418,7 +5400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>324</v>
       </c>
@@ -5538,7 +5520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>325</v>
       </c>
@@ -5660,7 +5642,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>326</v>
       </c>
@@ -5778,7 +5760,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>335</v>
       </c>
@@ -5896,7 +5878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>339</v>
       </c>
@@ -6015,24 +5997,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP38">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI37">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>